--- a/AAII_Financials/Quarterly/LGHL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LGHL_QTR_FIN.xlsx
@@ -1165,11 +1165,11 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>100</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
@@ -1515,10 +1515,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E20" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
@@ -1589,10 +1589,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E21" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="F21" s="3">
         <v>-3200</v>
@@ -2403,10 +2403,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="E32" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
@@ -2994,10 +2994,10 @@
         <v>500</v>
       </c>
       <c r="H43" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="I43" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="J43" s="3">
         <v>8400</v>
@@ -3142,10 +3142,10 @@
         <v>200</v>
       </c>
       <c r="H45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>1000</v>
@@ -4085,11 +4085,11 @@
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2700</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
